--- a/result/train_info_googlenet_part_detrend_plr_stft_bin_win.xlsx
+++ b/result/train_info_googlenet_part_detrend_plr_stft_bin_win.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3387520336622115</v>
+        <v>0.3588441469378625</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1512272692335075</v>
+        <v>0.1413270042514836</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9394277220364177</v>
+        <v>0.94611668524712</v>
       </c>
       <c r="F2" t="n">
-        <v>0.908121128699243</v>
+        <v>0.9293865905848787</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9781319495922906</v>
+        <v>0.9659006671608599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9418272662384012</v>
+        <v>0.9472918938567794</v>
       </c>
       <c r="I2" t="n">
-        <v>70.90517282485962</v>
+        <v>50.37044262886047</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1071649027710163</v>
+        <v>0.1077165182916528</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.055127304727928</v>
+        <v>0.0574552439368115</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9817911557041992</v>
+        <v>0.9812337421033073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9843517138599106</v>
+        <v>0.9846957820082121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9792438843587843</v>
+        <v>0.977761304670126</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9817911557041992</v>
+        <v>0.9812162916124233</v>
       </c>
       <c r="I3" t="n">
-        <v>70.34742617607117</v>
+        <v>51.59871339797974</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05550733829584156</v>
+        <v>0.05760794792329148</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0463559446627682</v>
+        <v>0.05675138072827114</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9856930509104422</v>
+        <v>0.9840208101077667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9784592917123037</v>
+        <v>0.9819188191881919</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.986286137879911</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9858377781864999</v>
+        <v>0.9840976331360947</v>
       </c>
       <c r="I4" t="n">
-        <v>70.5860652923584</v>
+        <v>51.43674230575562</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04171790997091235</v>
+        <v>0.03996172654959698</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03698886507232095</v>
+        <v>0.04033338423568987</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9875510962467484</v>
+        <v>0.986250464511334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9848875783265757</v>
+        <v>0.9812912692589876</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9903632320237212</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9876178155608945</v>
+        <v>0.9863569321533924</v>
       </c>
       <c r="I5" t="n">
-        <v>70.92646908760071</v>
+        <v>50.70330500602722</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02831900691470674</v>
+        <v>0.03511464117895079</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02579117467428541</v>
+        <v>0.06390333231180333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9920104050538833</v>
+        <v>0.9773318468970643</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9936779471922648</v>
+        <v>0.9766839378238342</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9903632320237212</v>
+        <v>0.9781319495922906</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9920178206794134</v>
+        <v>0.9774074074074074</v>
       </c>
       <c r="I6" t="n">
-        <v>71.9959888458252</v>
+        <v>50.9273898601532</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02437225988164667</v>
+        <v>0.02690207662547276</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02403299556132378</v>
+        <v>0.08936849049776076</v>
       </c>
       <c r="E7" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9715719063545151</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9896755162241888</v>
+        <v>0.9873611643048641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.955522609340252</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9922365988909427</v>
+        <v>0.9711810133735167</v>
       </c>
       <c r="I7" t="n">
-        <v>72.83021974563599</v>
+        <v>51.31669306755066</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02199204762557585</v>
+        <v>0.0205499752074633</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03269455380208746</v>
+        <v>0.01728933148791107</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9899665551839465</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9881831610044313</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9918458117123795</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9900110987791343</v>
+        <v>0.9949897940248654</v>
       </c>
       <c r="I8" t="n">
-        <v>73.3546724319458</v>
+        <v>51.40430760383606</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02304480967247372</v>
+        <v>0.02291231181715663</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04216894507683681</v>
+        <v>0.02281318931184577</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9842066146413972</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9906120916259857</v>
+        <v>0.9933234421364985</v>
       </c>
       <c r="G9" t="n">
-        <v>0.977761304670126</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9841447491139713</v>
+        <v>0.992955135335558</v>
       </c>
       <c r="I9" t="n">
-        <v>73.59244871139526</v>
+        <v>51.28934168815613</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01774481651987718</v>
+        <v>0.01945412309422705</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01652406036431699</v>
+        <v>0.03195970389129561</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9882943143812709</v>
       </c>
       <c r="F10" t="n">
-        <v>0.990791896869245</v>
+        <v>0.9906890130353817</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9939035654904859</v>
+        <v>0.988296488946684</v>
       </c>
       <c r="I10" t="n">
-        <v>74.12541818618774</v>
+        <v>51.50186967849731</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01540584452146047</v>
+        <v>0.01449257455866356</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0348939259491617</v>
+        <v>0.01845304299553735</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9888517279821628</v>
+        <v>0.9933110367892977</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9932685115931189</v>
+        <v>0.9959016393442623</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9844329132690882</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9888309754281459</v>
+        <v>0.9933110367892977</v>
       </c>
       <c r="I11" t="n">
-        <v>73.10926342010498</v>
+        <v>52.59804654121399</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01629020287125436</v>
+        <v>0.01383314248607786</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02598082556867333</v>
+        <v>0.02236848502469422</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9899665551839465</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9867452135493373</v>
+        <v>0.9903988183161004</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9900258588843739</v>
+        <v>0.9922308546059934</v>
       </c>
       <c r="I12" t="n">
-        <v>71.9381320476532</v>
+        <v>51.5799195766449</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01644143284274738</v>
+        <v>0.0175828795978375</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02367495338388749</v>
+        <v>0.02756333069575068</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9923820141211446</v>
+        <v>0.9931252322556671</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9929499072356215</v>
+        <v>0.9951618905842947</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9918458117123795</v>
+        <v>0.9911045218680504</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9923975523827183</v>
+        <v>0.9931290622098422</v>
       </c>
       <c r="I13" t="n">
-        <v>71.05905747413635</v>
+        <v>51.13855981826782</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0158246073569223</v>
+        <v>0.01347382285560061</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02397977073088608</v>
+        <v>0.0230160430961491</v>
       </c>
       <c r="E14" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F14" t="n">
-        <v>0.994415487714073</v>
+        <v>0.9904306220095693</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9921991084695394</v>
+        <v>0.9939058171745152</v>
       </c>
       <c r="I14" t="n">
-        <v>70.84743595123291</v>
+        <v>51.20902824401855</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01492315963550234</v>
+        <v>0.01485909656199013</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03113815676594517</v>
+        <v>0.01424378229912368</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9901523597175771</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9892711801701812</v>
+        <v>0.9940828402366864</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9911045218680504</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9901870024069617</v>
+        <v>0.9951869677897075</v>
       </c>
       <c r="I15" t="n">
-        <v>70.74641370773315</v>
+        <v>49.50030541419983</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01402900058915692</v>
+        <v>0.01137784356331092</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0152544174708437</v>
+        <v>0.02483414173330808</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9962797619047619</v>
+        <v>0.9911111111111112</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9944300037133309</v>
+        <v>0.9914783253056688</v>
       </c>
       <c r="I16" t="n">
-        <v>71.6579225063324</v>
+        <v>49.75724768638611</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01140361632614235</v>
+        <v>0.008394842640381045</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0208203932060309</v>
+        <v>0.01661258833204955</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9977586850952559</v>
+        <v>0.9919028340080972</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9938604651162791</v>
+        <v>0.9953831948291783</v>
       </c>
       <c r="I17" t="n">
-        <v>72.46883201599121</v>
+        <v>48.76372909545898</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01006028501129795</v>
+        <v>0.01256697241281527</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01839372660663701</v>
+        <v>0.04650975156107843</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9858788554440728</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9743125904486252</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9860856829000366</v>
       </c>
       <c r="I18" t="n">
-        <v>73.23372530937195</v>
+        <v>46.76225090026855</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01065853816379803</v>
+        <v>0.01186860843179002</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01673610659357771</v>
+        <v>0.0171198361422715</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9951744617668894</v>
+        <v>0.9940806511283758</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9944362017804155</v>
+        <v>0.99500092575449</v>
       </c>
       <c r="I19" t="n">
-        <v>73.28904247283936</v>
+        <v>47.61865043640137</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.009479412562923704</v>
+        <v>0.01236112424729283</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01887855737779383</v>
+        <v>0.02486235238219055</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.9920104050538833</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9886196769456681</v>
+        <v>0.9936779471922648</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9933603836222796</v>
+        <v>0.9920178206794134</v>
       </c>
       <c r="I20" t="n">
-        <v>73.08400058746338</v>
+        <v>47.67612624168396</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.008182310237173166</v>
+        <v>0.008872193369149552</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01641650774378223</v>
+        <v>0.02018576115942402</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9946116685247121</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9911667280088333</v>
+        <v>0.9911569638909359</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9946445060018467</v>
+        <v>0.9940872135994088</v>
       </c>
       <c r="I21" t="n">
-        <v>74.02520513534546</v>
+        <v>48.0545506477356</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.007144948925501631</v>
+        <v>0.008318864034930998</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0222509091998172</v>
+        <v>0.02575109906406101</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9940542549238202</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F22" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9897096655641309</v>
       </c>
       <c r="G22" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H22" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9939103155563758</v>
       </c>
       <c r="I22" t="n">
-        <v>72.84113049507141</v>
+        <v>48.26283597946167</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.009523306260977948</v>
+        <v>0.008156885718863001</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01574382258323142</v>
+        <v>0.0182710877618306</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9922394678492239</v>
+        <v>0.9940806511283758</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9937083641746854</v>
+        <v>0.99500092575449</v>
       </c>
       <c r="I23" t="n">
-        <v>72.40010809898376</v>
+        <v>48.13477516174316</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.005634227770526687</v>
+        <v>0.0075138042769128</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0204902154908069</v>
+        <v>0.01628949663942214</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9940542549238202</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F24" t="n">
-        <v>0.993338267949667</v>
+        <v>0.9940784603997039</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9940740740740741</v>
+        <v>0.9948148148148148</v>
       </c>
       <c r="I24" t="n">
-        <v>71.50480318069458</v>
+        <v>48.23831534385681</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.009548927325566312</v>
+        <v>0.009986518916986303</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0258397297799932</v>
+        <v>0.03182132406611086</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9929394277220365</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9893303899926417</v>
+        <v>0.9940387481371088</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9888806523350631</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9929837518463811</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="I25" t="n">
-        <v>71.01778674125671</v>
+        <v>49.30152249336243</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002521649749280422</v>
+        <v>0.01055802405814344</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02682473032967387</v>
+        <v>0.02246150189121019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9947974730583427</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9970215934475056</v>
+        <v>0.9922279792746114</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9947994056463596</v>
+        <v>0.9929629629629629</v>
       </c>
       <c r="I26" t="n">
-        <v>70.73378252983093</v>
+        <v>49.74621295928955</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.007361921568040487</v>
+        <v>0.004015397415647712</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02682969026660732</v>
+        <v>0.01356573465082449</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9968413229282794</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9893225331369662</v>
+        <v>0.9977720014853323</v>
       </c>
       <c r="G27" t="n">
         <v>0.9959229058561898</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9926117473217584</v>
+        <v>0.9968465961788165</v>
       </c>
       <c r="I27" t="n">
-        <v>71.81774997711182</v>
+        <v>52.43729281425476</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.006783877009578535</v>
+        <v>0.006783658613613134</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01237704750128722</v>
+        <v>0.01682945184596404</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9970337411939192</v>
+        <v>0.9940893978574067</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9968489341983318</v>
+        <v>0.9957446808510638</v>
       </c>
       <c r="I28" t="n">
-        <v>72.80018043518066</v>
+        <v>51.65226650238037</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.003262167869719232</v>
+        <v>0.007539413559808144</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01869912582187896</v>
+        <v>0.02347184723286515</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9926144756277696</v>
+        <v>0.9958924570575056</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9885100074128984</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9944506104328524</v>
+        <v>0.9921875</v>
       </c>
       <c r="I29" t="n">
-        <v>73.14579844474792</v>
+        <v>51.15474033355713</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.00623495982485486</v>
+        <v>0.004739959298497174</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03002634033879001</v>
+        <v>0.01288450667942866</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9914529914529915</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9929368029739777</v>
+        <v>0.9959289415247965</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9914625092798812</v>
+        <v>0.9966666666666667</v>
       </c>
       <c r="I30" t="n">
-        <v>73.10930895805359</v>
+        <v>48.80695295333862</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.00709833573174847</v>
+        <v>0.00474729327371592</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.009916386090125767</v>
+        <v>0.01934511812042411</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9962949240459429</v>
+        <v>0.9937037037037038</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9964795256624051</v>
+        <v>0.9940718784735088</v>
       </c>
       <c r="I31" t="n">
-        <v>73.20226049423218</v>
+        <v>48.76461935043335</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.006045379446786845</v>
+        <v>0.005742544881562135</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02552973336290283</v>
+        <v>0.02544429902220748</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9923820141211446</v>
+        <v>0.9936826458565589</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9871653832049871</v>
+        <v>0.9933333333333333</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9924423963133641</v>
+        <v>0.993701370878103</v>
       </c>
       <c r="I32" t="n">
-        <v>72.82592487335205</v>
+        <v>49.26460742950439</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.005643169125884057</v>
+        <v>0.006826454155952415</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01317610179258741</v>
+        <v>0.018236895110366</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9953548866592344</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9977653631284916</v>
+        <v>0.9937176644493718</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9929577464788732</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9953557495820174</v>
+        <v>0.9951887490747594</v>
       </c>
       <c r="I33" t="n">
-        <v>71.76393103599548</v>
+        <v>51.90622472763062</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.004600942567341504</v>
+        <v>0.005505804527089982</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01018796653686382</v>
+        <v>0.01497200268146202</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9970337411939192</v>
+        <v>0.9929915160457395</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9968489341983318</v>
+        <v>0.9953780735810686</v>
       </c>
       <c r="I34" t="n">
-        <v>71.18802118301392</v>
+        <v>51.78527879714966</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.004025264521146203</v>
+        <v>0.002661559713789505</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01779757527922612</v>
+        <v>0.02225700956323797</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9900808229243203</v>
+        <v>0.9981378026070763</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9944649446494465</v>
+        <v>0.9957272896154561</v>
       </c>
       <c r="I35" t="n">
-        <v>70.37559127807617</v>
+        <v>50.46706581115723</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.00269696082373223</v>
+        <v>0.003356720149917707</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.02366066806204944</v>
+        <v>0.01211063417427881</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9972129319955407</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9940520446096655</v>
+        <v>0.9974045235446792</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9911045218680504</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9925760950259837</v>
+        <v>0.9972196478220574</v>
       </c>
       <c r="I36" t="n">
-        <v>70.89642786979675</v>
+        <v>49.41833901405334</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.007716920710701384</v>
+        <v>0.004881443821590299</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01767115614980738</v>
+        <v>0.05339192440846974</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9864362690449647</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9966530308664932</v>
+        <v>0.9924953095684803</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.980355819125278</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9949879339149805</v>
+        <v>0.9863882155509975</v>
       </c>
       <c r="I37" t="n">
-        <v>72.21746325492859</v>
+        <v>50.78252959251404</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.003208277695189099</v>
+        <v>0.004722724888379324</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01350925514969319</v>
+        <v>0.02047680009335631</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F38" t="n">
-        <v>0.995197635759143</v>
+        <v>0.995919881305638</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H38" t="n">
-        <v>0.996854764107308</v>
+        <v>0.9955506117908788</v>
       </c>
       <c r="I38" t="n">
-        <v>72.13479232788086</v>
+        <v>50.84305357933044</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.004404632240444485</v>
+        <v>0.002760821823339884</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01721754877710807</v>
+        <v>0.0147881900964249</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9946116685247121</v>
+        <v>0.9964697138610182</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9900844656628718</v>
+        <v>0.9962949240459429</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9992587101556709</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9946504334993543</v>
+        <v>0.9964795256624051</v>
       </c>
       <c r="I39" t="n">
-        <v>72.27492356300354</v>
+        <v>51.36033463478088</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.002494319430116001</v>
+        <v>0.001067990023914394</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.008794590759711646</v>
+        <v>0.01908563864767072</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9981419546636938</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9962880475129918</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9955489614243324</v>
       </c>
       <c r="I40" t="n">
-        <v>72.86245679855347</v>
+        <v>50.94597172737122</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.002391960553980143</v>
+        <v>0.004741304137402029</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01591528874172657</v>
+        <v>0.02585234829247701</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9966592427616926</v>
+        <v>0.9940784603997039</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H41" t="n">
-        <v>0.995919881305638</v>
+        <v>0.9948148148148148</v>
       </c>
       <c r="I41" t="n">
-        <v>73.15448641777039</v>
+        <v>50.70283269882202</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.004847875665014175</v>
+        <v>0.005694907135836647</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.02298650842805308</v>
+        <v>0.01791127580947658</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9977586850952559</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9938604651162791</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="I42" t="n">
-        <v>73.29266977310181</v>
+        <v>47.72691607475281</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.002537660221342772</v>
+        <v>0.001530117134567036</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02031373279009906</v>
+        <v>0.01442532584360648</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9951690821256038</v>
+        <v>0.9968413229282794</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9985074626865672</v>
+        <v>0.9974025974025974</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9918458117123795</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H43" t="n">
-        <v>0.995165489029379</v>
+        <v>0.9968477656221028</v>
       </c>
       <c r="I43" t="n">
-        <v>72.39226055145264</v>
+        <v>49.23492813110352</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.003046368856222077</v>
+        <v>0.003459460210556981</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01200188506950138</v>
+        <v>0.01860134285080681</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9972129319955407</v>
+        <v>0.9936826458565589</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9963004069552349</v>
+        <v>0.9886280264123257</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9972227365302722</v>
+        <v>0.9937315634218289</v>
       </c>
       <c r="I44" t="n">
-        <v>71.37134051322937</v>
+        <v>50.94440293312073</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.002666630711611277</v>
+        <v>0.004683447809767357</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01189005787346535</v>
+        <v>0.01524641009070725</v>
       </c>
       <c r="E45" t="n">
-        <v>0.99702712746191</v>
+        <v>0.9960981047937569</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9966666666666667</v>
+        <v>0.9966604823747681</v>
       </c>
       <c r="G45" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9970359392367544</v>
+        <v>0.9961060634155386</v>
       </c>
       <c r="I45" t="n">
-        <v>70.53870797157288</v>
+        <v>50.89661574363708</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.00167642701366449</v>
+        <v>0.000178582913918204</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01997886098742715</v>
+        <v>0.01863355167734106</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9940542549238202</v>
+        <v>0.99702712746191</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9904341427520236</v>
+        <v>0.9951994091580503</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9940915805022157</v>
+        <v>0.997040325564188</v>
       </c>
       <c r="I46" t="n">
-        <v>70.55477094650269</v>
+        <v>51.48877215385437</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.001098281409195856</v>
+        <v>0.003186944523333111</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01325399297486496</v>
+        <v>0.01500541858846976</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9985124581628858</v>
+        <v>0.9948263118994827</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9968442546872099</v>
+        <v>0.996299037749815</v>
       </c>
       <c r="I47" t="n">
-        <v>70.79400420188904</v>
+        <v>51.78746914863586</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.002565788641344555</v>
+        <v>0.002193471134443047</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01182069240069631</v>
+        <v>0.01346237737893259</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9981454005934718</v>
+        <v>0.9959364610269671</v>
       </c>
       <c r="G48" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9992587101556709</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9977753058954394</v>
+        <v>0.9975948196114709</v>
       </c>
       <c r="I48" t="n">
-        <v>71.47641658782959</v>
+        <v>50.97806739807129</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.002914239282194898</v>
+        <v>0.001023722529882223</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01092318282284928</v>
+        <v>0.01722348354365674</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9983277591973244</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9988868274582561</v>
+        <v>0.9900735294117647</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9983311700352309</v>
+        <v>0.994093761535622</v>
       </c>
       <c r="I49" t="n">
-        <v>72.6255145072937</v>
+        <v>51.61575055122375</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.001773227067733144</v>
+        <v>0.002858959463885069</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.01997165044635492</v>
+        <v>0.013596202957666</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9923820141211446</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9966355140186915</v>
+        <v>0.9966617210682492</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9881393624907339</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9923692536757863</v>
+        <v>0.996292176492399</v>
       </c>
       <c r="I50" t="n">
-        <v>72.47673511505127</v>
+        <v>51.02603316307068</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.001769101841555001</v>
+        <v>0.004145882201383347</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01474099275937396</v>
+        <v>0.01576818255202637</v>
       </c>
       <c r="E51" t="n">
         <v>0.9959123002601263</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9940915805022157</v>
+        <v>0.9970282317979198</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9959304476507584</v>
+        <v>0.9959183673469387</v>
       </c>
       <c r="I51" t="n">
-        <v>72.7799026966095</v>
+        <v>51.21087908744812</v>
       </c>
     </row>
   </sheetData>
